--- a/html/rules.xlsx
+++ b/html/rules.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naoki\Desktop\code\journal_abbreviation\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A03352-11A5-456C-8763-05AC509A3100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9544DCAD-7852-49CD-9AF2-3E284B4F1094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A59892AB-739F-49FA-9B59-E8BCB2D1CAF6}"/>
   </bookViews>
   <sheets>
-    <sheet name="journal" sheetId="1" r:id="rId1"/>
+    <sheet name="title" sheetId="1" r:id="rId1"/>
     <sheet name="month" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">journal!$A$1:$B$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">title!$A$1:$B$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
